--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="77">
   <si>
     <t>Код</t>
   </si>
@@ -31,7 +31,7 @@
     <t>F1</t>
   </si>
   <si>
-    <t>На сайте новый клиент видит список доступных депозитов с актуальными ставками</t>
+    <t>На сайте новый клиент видит на сайте список доступных депозитов с актуальными ставками</t>
   </si>
   <si>
     <t>F2</t>
@@ -43,43 +43,49 @@
     <t>F3</t>
   </si>
   <si>
-    <t>Менеджер может изучить заявку в системе кол-центра</t>
+    <t>Сотрудник колл-центра должен иметь возможность просмотра заявки с сайта</t>
   </si>
   <si>
     <t>F4</t>
   </si>
   <si>
+    <t>Сотрудник колл-центра должен иметь возможность дополнения заявки на основе данных звонка</t>
+  </si>
+  <si>
+    <t>F5</t>
+  </si>
+  <si>
     <t>В интернет-банке клиент видит список доступных депозитов с актуальными ставками и персонализированные ставки лично для него</t>
   </si>
   <si>
-    <t>F5</t>
+    <t>F6</t>
   </si>
   <si>
     <t>Указав счёт и сумму депозита, клиент может подать заявку на открытие депозита через интернет-банк</t>
   </si>
   <si>
-    <t>F6</t>
+    <t>F7</t>
   </si>
   <si>
     <t>Со ставками по депозитам должны иметь возможность работать сотрудники как бэк-офиса депозитов, так и бэк-офиса кредитов</t>
   </si>
   <si>
-    <t>F7</t>
+    <t>F8</t>
   </si>
   <si>
     <t>На этапе MVP предполагается, что заявку на открытие депозита обработает менеджер в бэк-офисе. Он подтвердит условия депозита в АБС банка</t>
   </si>
   <si>
-    <t>F8</t>
+    <t>F9</t>
   </si>
   <si>
     <t>Клиент должен получить СМС-уведомления после подтверждения размера ставки и открытия депозита</t>
   </si>
   <si>
-    <t>F9</t>
-  </si>
-  <si>
-    <t>Возможно, стоит реализовать в АБС весь текущий процесс согласования ставки по заявке</t>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>Возможно, стоит реализовать в АБС весь текущий процесс согласования ставки по заявке (не в рамках MVP)</t>
   </si>
   <si>
     <t>U</t>
@@ -190,7 +196,7 @@
     <t>+R2.1</t>
   </si>
   <si>
-    <t>Функционал работы с СМС реализован в ядре системы. Он требует доработки со стороны подрядчика, но этого лучше избежать. Реализовать такой бизнес-функционал можно силами команды разработки банка</t>
+    <t>Функционал работы с СМС реализован в ядре системы интернет-банка. Он требует доработки со стороны подрядчика, но этого лучше избежать. Реализовать такой бизнес-функционал можно силами команды разработки банка</t>
   </si>
   <si>
     <t>+R2.2</t>
@@ -1579,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr defaultColWidth="10.6" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.6016" style="1" customWidth="1"/>
@@ -1628,7 +1634,7 @@
       <c r="D4" s="9"/>
       <c r="E4" s="6"/>
     </row>
-    <row r="5" ht="17.45" customHeight="1">
+    <row r="5" ht="32.45" customHeight="1">
       <c r="A5" s="4"/>
       <c r="B5" t="s" s="7">
         <v>5</v>
@@ -1716,61 +1722,61 @@
       <c r="D12" s="14"/>
       <c r="E12" s="6"/>
     </row>
-    <row r="13" ht="32.45" customHeight="1">
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" t="s" s="12">
         <v>21</v>
       </c>
-      <c r="C13" t="s" s="10">
+      <c r="C13" t="s" s="13">
         <v>22</v>
       </c>
-      <c r="D13" s="11"/>
+      <c r="D13" s="14"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" ht="30" customHeight="1">
+    <row r="14" ht="32.45" customHeight="1">
       <c r="A14" s="4"/>
-      <c r="B14" t="s" s="7">
+      <c r="B14" t="s" s="12">
         <v>23</v>
       </c>
-      <c r="C14" t="s" s="8">
+      <c r="C14" t="s" s="10">
         <v>24</v>
       </c>
-      <c r="D14" s="9"/>
+      <c r="D14" s="11"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" ht="39" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="4"/>
       <c r="B15" t="s" s="7">
         <v>25</v>
       </c>
-      <c r="C15" t="s" s="10">
+      <c r="C15" t="s" s="8">
         <v>26</v>
       </c>
-      <c r="D15" t="s" s="15">
+      <c r="D15" s="9"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" ht="39" customHeight="1">
+      <c r="A16" s="4"/>
+      <c r="B16" t="s" s="7">
         <v>27</v>
       </c>
-      <c r="E15" s="6"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" t="s" s="12">
+      <c r="C16" t="s" s="10">
         <v>28</v>
       </c>
-      <c r="C16" t="s" s="10">
+      <c r="D16" t="s" s="15">
         <v>29</v>
       </c>
-      <c r="D16" s="11"/>
       <c r="E16" s="6"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="4"/>
-      <c r="B17" t="s" s="7">
+      <c r="B17" t="s" s="12">
         <v>30</v>
       </c>
-      <c r="C17" t="s" s="8">
+      <c r="C17" t="s" s="10">
         <v>31</v>
       </c>
-      <c r="D17" s="9"/>
+      <c r="D17" s="11"/>
       <c r="E17" s="6"/>
     </row>
     <row r="18" ht="30" customHeight="1">
@@ -1778,15 +1784,15 @@
       <c r="B18" t="s" s="7">
         <v>32</v>
       </c>
-      <c r="C18" t="s" s="10">
+      <c r="C18" t="s" s="8">
         <v>33</v>
       </c>
-      <c r="D18" s="11"/>
+      <c r="D18" s="9"/>
       <c r="E18" s="6"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="4"/>
-      <c r="B19" t="s" s="12">
+      <c r="B19" t="s" s="7">
         <v>34</v>
       </c>
       <c r="C19" t="s" s="10">
@@ -1797,13 +1803,13 @@
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="4"/>
-      <c r="B20" t="s" s="7">
+      <c r="B20" t="s" s="12">
         <v>36</v>
       </c>
-      <c r="C20" t="s" s="8">
+      <c r="C20" t="s" s="10">
         <v>37</v>
       </c>
-      <c r="D20" s="9"/>
+      <c r="D20" s="11"/>
       <c r="E20" s="6"/>
     </row>
     <row r="21" ht="30" customHeight="1">
@@ -1811,15 +1817,15 @@
       <c r="B21" t="s" s="7">
         <v>38</v>
       </c>
-      <c r="C21" t="s" s="10">
+      <c r="C21" t="s" s="8">
         <v>39</v>
       </c>
-      <c r="D21" s="11"/>
+      <c r="D21" s="9"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" ht="62.45" customHeight="1">
+    <row r="22" ht="30" customHeight="1">
       <c r="A22" s="4"/>
-      <c r="B22" t="s" s="12">
+      <c r="B22" t="s" s="7">
         <v>40</v>
       </c>
       <c r="C22" t="s" s="10">
@@ -1828,15 +1834,15 @@
       <c r="D22" s="11"/>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" ht="30" customHeight="1">
+    <row r="23" ht="62.45" customHeight="1">
       <c r="A23" s="4"/>
-      <c r="B23" t="s" s="7">
+      <c r="B23" t="s" s="12">
         <v>42</v>
       </c>
-      <c r="C23" t="s" s="8">
+      <c r="C23" t="s" s="10">
         <v>43</v>
       </c>
-      <c r="D23" s="9"/>
+      <c r="D23" s="11"/>
       <c r="E23" s="6"/>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -1844,59 +1850,59 @@
       <c r="B24" t="s" s="7">
         <v>44</v>
       </c>
-      <c r="C24" t="s" s="10">
+      <c r="C24" t="s" s="8">
         <v>45</v>
       </c>
-      <c r="D24" t="s" s="15">
-        <v>46</v>
-      </c>
+      <c r="D24" s="9"/>
       <c r="E24" s="6"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="4"/>
       <c r="B25" t="s" s="7">
+        <v>46</v>
+      </c>
+      <c r="C25" t="s" s="10">
         <v>47</v>
       </c>
-      <c r="C25" t="s" s="8">
+      <c r="D25" t="s" s="15">
         <v>48</v>
       </c>
-      <c r="D25" s="9"/>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" ht="35.25" customHeight="1">
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="4"/>
-      <c r="B26" s="16"/>
-      <c r="C26" t="s" s="17">
+      <c r="B26" t="s" s="7">
         <v>49</v>
       </c>
-      <c r="D26" s="18"/>
+      <c r="C26" t="s" s="8">
+        <v>50</v>
+      </c>
+      <c r="D26" s="9"/>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" ht="92.45" customHeight="1">
+    <row r="27" ht="35.25" customHeight="1">
       <c r="A27" s="4"/>
-      <c r="B27" t="s" s="7">
-        <v>50</v>
-      </c>
-      <c r="C27" t="s" s="10">
+      <c r="B27" s="16"/>
+      <c r="C27" t="s" s="17">
         <v>51</v>
       </c>
-      <c r="D27" t="s" s="15">
-        <v>52</v>
-      </c>
+      <c r="D27" s="18"/>
       <c r="E27" s="6"/>
     </row>
-    <row r="28" ht="47.45" customHeight="1">
+    <row r="28" ht="92.45" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" t="s" s="7">
+        <v>52</v>
+      </c>
+      <c r="C28" t="s" s="10">
         <v>53</v>
       </c>
-      <c r="C28" t="s" s="10">
+      <c r="D28" t="s" s="15">
         <v>54</v>
       </c>
-      <c r="D28" s="11"/>
       <c r="E28" s="6"/>
     </row>
-    <row r="29" ht="32.45" customHeight="1">
+    <row r="29" ht="47.45" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" t="s" s="7">
         <v>55</v>
@@ -1907,27 +1913,27 @@
       <c r="D29" s="11"/>
       <c r="E29" s="6"/>
     </row>
-    <row r="30" ht="33" customHeight="1">
+    <row r="30" ht="32.45" customHeight="1">
       <c r="A30" s="4"/>
-      <c r="B30" s="16"/>
-      <c r="C30" t="s" s="17">
+      <c r="B30" t="s" s="7">
         <v>57</v>
       </c>
-      <c r="D30" s="18"/>
+      <c r="C30" t="s" s="10">
+        <v>58</v>
+      </c>
+      <c r="D30" s="11"/>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" ht="47.45" customHeight="1">
+    <row r="31" ht="33" customHeight="1">
       <c r="A31" s="4"/>
-      <c r="B31" t="s" s="7">
-        <v>58</v>
-      </c>
-      <c r="C31" t="s" s="10">
+      <c r="B31" s="16"/>
+      <c r="C31" t="s" s="17">
         <v>59</v>
       </c>
-      <c r="D31" s="11"/>
+      <c r="D31" s="18"/>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" ht="32.45" customHeight="1">
+    <row r="32" ht="47.45" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" t="s" s="7">
         <v>60</v>
@@ -1935,40 +1941,40 @@
       <c r="C32" t="s" s="10">
         <v>61</v>
       </c>
-      <c r="D32" t="s" s="15">
-        <v>62</v>
-      </c>
+      <c r="D32" s="11"/>
       <c r="E32" s="6"/>
     </row>
     <row r="33" ht="32.45" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" t="s" s="7">
+        <v>62</v>
+      </c>
+      <c r="C33" t="s" s="10">
         <v>63</v>
       </c>
-      <c r="C33" t="s" s="10">
+      <c r="D33" t="s" s="15">
         <v>64</v>
       </c>
-      <c r="D33" s="11"/>
       <c r="E33" s="6"/>
     </row>
-    <row r="34" ht="33" customHeight="1">
+    <row r="34" ht="32.45" customHeight="1">
       <c r="A34" s="4"/>
-      <c r="B34" s="16"/>
-      <c r="C34" t="s" s="17">
+      <c r="B34" t="s" s="7">
         <v>65</v>
       </c>
-      <c r="D34" s="18"/>
+      <c r="C34" t="s" s="10">
+        <v>66</v>
+      </c>
+      <c r="D34" s="11"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="35" ht="32.45" customHeight="1">
+    <row r="35" ht="33" customHeight="1">
       <c r="A35" s="4"/>
-      <c r="B35" t="s" s="7">
-        <v>66</v>
-      </c>
-      <c r="C35" t="s" s="10">
+      <c r="B35" s="16"/>
+      <c r="C35" t="s" s="17">
         <v>67</v>
       </c>
-      <c r="D35" s="11"/>
+      <c r="D35" s="18"/>
       <c r="E35" s="6"/>
     </row>
     <row r="36" ht="32.45" customHeight="1">
@@ -1982,7 +1988,7 @@
       <c r="D36" s="11"/>
       <c r="E36" s="6"/>
     </row>
-    <row r="37" ht="62.45" customHeight="1">
+    <row r="37" ht="32.45" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" t="s" s="7">
         <v>70</v>
@@ -1993,38 +1999,49 @@
       <c r="D37" s="11"/>
       <c r="E37" s="6"/>
     </row>
-    <row r="38" ht="33" customHeight="1">
+    <row r="38" ht="62.45" customHeight="1">
       <c r="A38" s="4"/>
-      <c r="B38" s="16"/>
-      <c r="C38" t="s" s="17">
+      <c r="B38" t="s" s="7">
         <v>72</v>
       </c>
-      <c r="D38" s="18"/>
+      <c r="C38" t="s" s="10">
+        <v>73</v>
+      </c>
+      <c r="D38" s="11"/>
       <c r="E38" s="6"/>
     </row>
     <row r="39" ht="33" customHeight="1">
       <c r="A39" s="4"/>
-      <c r="B39" t="s" s="7">
-        <v>73</v>
-      </c>
-      <c r="C39" t="s" s="10">
+      <c r="B39" s="16"/>
+      <c r="C39" t="s" s="17">
         <v>74</v>
       </c>
-      <c r="D39" s="11"/>
+      <c r="D39" s="18"/>
       <c r="E39" s="6"/>
+    </row>
+    <row r="40" ht="33" customHeight="1">
+      <c r="A40" s="4"/>
+      <c r="B40" t="s" s="7">
+        <v>75</v>
+      </c>
+      <c r="C40" t="s" s="10">
+        <v>76</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C24:D24"/>
     <mergeCell ref="C26:D26"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C39:D39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811" footer="0.511811"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>

--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="79">
   <si>
     <t>Код</t>
   </si>
@@ -79,13 +79,13 @@
     <t>F9</t>
   </si>
   <si>
-    <t>Клиент должен получить СМС-уведомления после подтверждения размера ставки и открытия депозита</t>
+    <t>Операцию подачи заявки на открытие депозита через интернет-банк должна быть подтверждена с помощью СМС-кода</t>
   </si>
   <si>
     <t>F10</t>
   </si>
   <si>
-    <t>Возможно, стоит реализовать в АБС весь текущий процесс согласования ставки по заявке (не в рамках MVP)</t>
+    <t>Реализовать в АБС весь текущий процесс согласования ставки по заявке. Добавление заявок из других систем и АБС, просмотр заявок ответственными сотрудниками, подтверждение/отклонение заявки, архивирование заявок.</t>
   </si>
   <si>
     <t>U</t>
@@ -97,7 +97,7 @@
     <t>U1</t>
   </si>
   <si>
-    <t>Операцию подачи заявки на открытие депозита через интернет-банк необходимо будет подтвердить с помощью СМС-кода</t>
+    <t>Чтобы клиенту не нужно было ехать в банк или выпускать УКЭП для открытия депозита должна быть реализована возможность подписать заявление простой электронной подписью ПЭП через СМС</t>
   </si>
   <si>
     <t>Если это требование рассматривать в контексте безопасности, то его также можно отнести к ограничениям реализации</t>
@@ -106,7 +106,7 @@
     <t>U2</t>
   </si>
   <si>
-    <t>Нужно придерживаться системы дизайна для приложений, которая принята в компании</t>
+    <t>Использовать брэнд-бук компании и/или использовать утвержденные элементы дизайна</t>
   </si>
   <si>
     <t>R</t>
@@ -118,13 +118,13 @@
     <t>R1</t>
   </si>
   <si>
-    <t>Все сервисы должны работать 24/7 и быть доступны в 99,9% случаев</t>
+    <t>График работы: Все сервисы должны работать 24/7</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>В случае сбоев в ЦОД необходимо, чтобы сервисы интернет-банка были доступны и выдерживали требуемую нагрузку</t>
+    <t>Система должна обеспечивать доступность 99.95% (то есть, 21 минута 54 секунды возможного простоя в месяц) c RTO 30 минут</t>
   </si>
   <si>
     <t>P</t>
@@ -136,13 +136,19 @@
     <t>P1</t>
   </si>
   <si>
-    <t>Отклик по всем операциям в интерфейсах клиента и сотрудников должен занимать миллисекунды</t>
+    <t>Отклик по всем операциям в интерфейсах клиента и сотрудников должен занимать не более 500 миллисекунд</t>
   </si>
   <si>
     <t>P2</t>
   </si>
   <si>
-    <t>Лучше предусмотреть равномерное горизонтальное масштабирование и распределение запросов между серверами, приложениями и ЦОД. Но нужно учитывать, что АБС может масштабироваться только вертикально из-за своей базы данных.</t>
+    <t>Системы Сайта и Интернет-банка должны выдерживать в пике 300RPS</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Система АБС должны выдерживать в пике 100RPS</t>
   </si>
   <si>
     <t>S</t>
@@ -154,7 +160,7 @@
     <t>S1</t>
   </si>
   <si>
-    <t>Нужно предусмотреть разработку документации для дальнейшего расширения системы</t>
+    <t>Нужно предусмотреть разработку документации для дальнейшего расширения системы. Документация должна быть представлена в виде диайграмм C4, ER и ADR в репозиториях соответствующих проектов</t>
   </si>
   <si>
     <t>Уточнить состав и формат документации</t>
@@ -166,9 +172,6 @@
     <t>+ Ограничения (Restricitions)</t>
   </si>
   <si>
-    <t>Ограничения проектирования</t>
-  </si>
-  <si>
     <t>+R1.1</t>
   </si>
   <si>
@@ -190,9 +193,6 @@
     <t>Возможно, стоит подумать о переводе интернет-банка на микросервисную архитектуру, но пока только в рамках задачи открытия депозитов</t>
   </si>
   <si>
-    <t>Ограничения реализации</t>
-  </si>
-  <si>
     <t>+R2.1</t>
   </si>
   <si>
@@ -214,28 +214,34 @@
     <t>Фактически приложения работают в одном ЦОД на одной группе серверов. У банка есть резервный ЦОД, в случае сбоя можно переключиться на него</t>
   </si>
   <si>
-    <t>Требования к интерфейсам (системным)</t>
+    <t>+R2.4</t>
+  </si>
+  <si>
+    <t>АБС может масштабироваться только вертикально из-за своей базы данных</t>
   </si>
   <si>
     <t>+R3.1</t>
   </si>
   <si>
-    <t>Стоит учитывать, что с сайта передаётся чувствительная информация. Данные необходимо защищать с помощью механизма шифрования трафика</t>
+    <t>Стоит учитывать, что с сайта передаётся чувствительная информация. Данные необходимо защищать с помощью механизма шифрования трафика TLS 1.2</t>
   </si>
   <si>
     <t>+R3.2</t>
   </si>
   <si>
-    <t>В интернет-банке данные при передаче надо защитить каким-то механизмом шифрования</t>
+    <t>В интернет-банке данные при передаче надо защитить механизмом шифрования TLS 1.2</t>
   </si>
   <si>
     <t>+R3.3</t>
   </si>
   <si>
-    <t>Команда АБС утверждает, что база данных системы уже перегружена. Онлайн-подача заявок на большое количество продуктов может поставить под угрозу работоспособность банка. Поэтому лучше избежать прямой работы интернет-банка с API АБС в новом процессе</t>
-  </si>
-  <si>
-    <t>Физические ограничения</t>
+    <t>Невозможно работать с API АБС напрямую из-за требований к производительности и масштабируемости системы АБС</t>
+  </si>
+  <si>
+    <t>+R3.4</t>
+  </si>
+  <si>
+    <t>Система должна соответствовать 152-ФЗ</t>
   </si>
   <si>
     <t>+R4.1</t>
@@ -290,7 +296,7 @@
       <name val="Liberation Sans"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,12 +324,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="12"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="14"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -443,7 +443,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -492,15 +492,6 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="6" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -523,7 +514,6 @@
       <rgbColor rgb="ffececec"/>
       <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ff335593"/>
-      <rgbColor rgb="ffd2d2d2"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1585,7 +1575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr defaultColWidth="10.6" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.6016" style="1" customWidth="1"/>
@@ -1733,7 +1723,7 @@
       <c r="D13" s="14"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" ht="32.45" customHeight="1">
+    <row r="14" ht="47.45" customHeight="1">
       <c r="A14" s="4"/>
       <c r="B14" t="s" s="12">
         <v>23</v>
@@ -1755,7 +1745,7 @@
       <c r="D15" s="9"/>
       <c r="E15" s="6"/>
     </row>
-    <row r="16" ht="39" customHeight="1">
+    <row r="16" ht="47.45" customHeight="1">
       <c r="A16" s="4"/>
       <c r="B16" t="s" s="7">
         <v>27</v>
@@ -1823,7 +1813,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="22" ht="30" customHeight="1">
+    <row r="22" ht="32.45" customHeight="1">
       <c r="A22" s="4"/>
       <c r="B22" t="s" s="7">
         <v>40</v>
@@ -1834,7 +1824,7 @@
       <c r="D22" s="11"/>
       <c r="E22" s="6"/>
     </row>
-    <row r="23" ht="62.45" customHeight="1">
+    <row r="23" ht="17.45" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" t="s" s="12">
         <v>42</v>
@@ -1845,15 +1835,15 @@
       <c r="D23" s="11"/>
       <c r="E23" s="6"/>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="17.45" customHeight="1">
       <c r="A24" s="4"/>
-      <c r="B24" t="s" s="7">
+      <c r="B24" t="s" s="12">
         <v>44</v>
       </c>
-      <c r="C24" t="s" s="8">
+      <c r="C24" t="s" s="10">
         <v>45</v>
       </c>
-      <c r="D24" s="9"/>
+      <c r="D24" s="11"/>
       <c r="E24" s="6"/>
     </row>
     <row r="25" ht="30" customHeight="1">
@@ -1861,54 +1851,56 @@
       <c r="B25" t="s" s="7">
         <v>46</v>
       </c>
-      <c r="C25" t="s" s="10">
+      <c r="C25" t="s" s="8">
         <v>47</v>
       </c>
-      <c r="D25" t="s" s="15">
-        <v>48</v>
-      </c>
+      <c r="D25" s="9"/>
       <c r="E25" s="6"/>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="47.45" customHeight="1">
       <c r="A26" s="4"/>
       <c r="B26" t="s" s="7">
+        <v>48</v>
+      </c>
+      <c r="C26" t="s" s="10">
         <v>49</v>
       </c>
-      <c r="C26" t="s" s="8">
+      <c r="D26" t="s" s="15">
         <v>50</v>
       </c>
-      <c r="D26" s="9"/>
       <c r="E26" s="6"/>
     </row>
-    <row r="27" ht="35.25" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="4"/>
-      <c r="B27" s="16"/>
-      <c r="C27" t="s" s="17">
+      <c r="B27" t="s" s="7">
         <v>51</v>
       </c>
-      <c r="D27" s="18"/>
+      <c r="C27" t="s" s="8">
+        <v>52</v>
+      </c>
+      <c r="D27" s="9"/>
       <c r="E27" s="6"/>
     </row>
     <row r="28" ht="92.45" customHeight="1">
       <c r="A28" s="4"/>
       <c r="B28" t="s" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C28" t="s" s="10">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D28" t="s" s="15">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E28" s="6"/>
     </row>
     <row r="29" ht="47.45" customHeight="1">
       <c r="A29" s="4"/>
       <c r="B29" t="s" s="7">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C29" t="s" s="10">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D29" s="11"/>
       <c r="E29" s="6"/>
@@ -1916,74 +1908,78 @@
     <row r="30" ht="32.45" customHeight="1">
       <c r="A30" s="4"/>
       <c r="B30" t="s" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s" s="10">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D30" s="11"/>
       <c r="E30" s="6"/>
     </row>
-    <row r="31" ht="33" customHeight="1">
+    <row r="31" ht="47.45" customHeight="1">
       <c r="A31" s="4"/>
-      <c r="B31" s="16"/>
-      <c r="C31" t="s" s="17">
-        <v>59</v>
-      </c>
-      <c r="D31" s="18"/>
+      <c r="B31" t="s" s="7">
+        <v>60</v>
+      </c>
+      <c r="C31" t="s" s="10">
+        <v>61</v>
+      </c>
+      <c r="D31" s="11"/>
       <c r="E31" s="6"/>
     </row>
-    <row r="32" ht="47.45" customHeight="1">
+    <row r="32" ht="32.45" customHeight="1">
       <c r="A32" s="4"/>
       <c r="B32" t="s" s="7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s" s="10">
-        <v>61</v>
-      </c>
-      <c r="D32" s="11"/>
+        <v>63</v>
+      </c>
+      <c r="D32" t="s" s="15">
+        <v>64</v>
+      </c>
       <c r="E32" s="6"/>
     </row>
     <row r="33" ht="32.45" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" t="s" s="7">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C33" t="s" s="10">
-        <v>63</v>
-      </c>
-      <c r="D33" t="s" s="15">
-        <v>64</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="D33" s="11"/>
       <c r="E33" s="6"/>
     </row>
-    <row r="34" ht="32.45" customHeight="1">
+    <row r="34" ht="17.45" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" t="s" s="7">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s" s="10">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D34" s="11"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="35" ht="33" customHeight="1">
+    <row r="35" ht="32.45" customHeight="1">
       <c r="A35" s="4"/>
-      <c r="B35" s="16"/>
-      <c r="C35" t="s" s="17">
-        <v>67</v>
-      </c>
-      <c r="D35" s="18"/>
+      <c r="B35" t="s" s="7">
+        <v>69</v>
+      </c>
+      <c r="C35" t="s" s="10">
+        <v>70</v>
+      </c>
+      <c r="D35" s="11"/>
       <c r="E35" s="6"/>
     </row>
     <row r="36" ht="32.45" customHeight="1">
       <c r="A36" s="4"/>
       <c r="B36" t="s" s="7">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C36" t="s" s="10">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D36" s="11"/>
       <c r="E36" s="6"/>
@@ -1991,57 +1987,44 @@
     <row r="37" ht="32.45" customHeight="1">
       <c r="A37" s="4"/>
       <c r="B37" t="s" s="7">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s" s="10">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D37" s="11"/>
       <c r="E37" s="6"/>
     </row>
-    <row r="38" ht="62.45" customHeight="1">
+    <row r="38" ht="17.45" customHeight="1">
       <c r="A38" s="4"/>
       <c r="B38" t="s" s="7">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s" s="10">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D38" s="11"/>
       <c r="E38" s="6"/>
     </row>
     <row r="39" ht="33" customHeight="1">
       <c r="A39" s="4"/>
-      <c r="B39" s="16"/>
-      <c r="C39" t="s" s="17">
-        <v>74</v>
-      </c>
-      <c r="D39" s="18"/>
+      <c r="B39" t="s" s="7">
+        <v>77</v>
+      </c>
+      <c r="C39" t="s" s="10">
+        <v>78</v>
+      </c>
+      <c r="D39" s="11"/>
       <c r="E39" s="6"/>
     </row>
-    <row r="40" ht="33" customHeight="1">
-      <c r="A40" s="4"/>
-      <c r="B40" t="s" s="7">
-        <v>75</v>
-      </c>
-      <c r="C40" t="s" s="10">
-        <v>76</v>
-      </c>
-      <c r="D40" s="11"/>
-      <c r="E40" s="6"/>
-    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="6">
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C39:D39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811" footer="0.511811"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
